--- a/output/pdf_financials_xlsx/ZDC.xlsx
+++ b/output/pdf_financials_xlsx/ZDC.xlsx
@@ -47149,10 +47149,10 @@
         </is>
       </c>
       <c r="P437" s="5" t="n">
-        <v>5.998</v>
+        <v>-5.998</v>
       </c>
       <c r="Q437" s="5" t="n">
-        <v>5.998</v>
+        <v>-5.998</v>
       </c>
       <c r="R437" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ZDC.xlsx
+++ b/output/pdf_financials_xlsx/ZDC.xlsx
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.042502</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.011552</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -2283,31 +2283,31 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.955</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.761</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.474</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.763</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.042502</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.011552</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2403,31 +2403,31 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.955</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.761</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.474</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5.763</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.258008</v>
+        <v>0.215506</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.233663</v>
+        <v>0.222111</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -3123,31 +3123,31 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>14.165</v>
+        <v>11.21</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.705</v>
+        <v>0.872</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.581</v>
+        <v>0.42</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.71</v>
+        <v>0.54</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.634</v>
+        <v>0.873</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.916</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.528</v>
+        <v>0.957</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.694</v>
+        <v>1.22</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>7.24</v>
+        <v>1.477</v>
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">

--- a/output/pdf_financials_xlsx/ZDC.xlsx
+++ b/output/pdf_financials_xlsx/ZDC.xlsx
@@ -1975,16 +1975,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.368174</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.2757</v>
+        <v>0.609994</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.678</v>
+        <v>0.776</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.005</v>
+        <v>1.113</v>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
@@ -1992,31 +1992,31 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.661</v>
+        <v>0.847</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.66</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.66</v>
+        <v>0.788</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.44</v>
+        <v>1.924</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>1.335</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.791</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>1.188</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>4.863</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>7.109</v>
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.375662</v>
+        <v>0.7438360000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.337063</v>
+        <v>2.671357</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.079</v>
+        <v>1.177</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.358</v>
+        <v>5.466</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2048,31 +2048,31 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-26.082</v>
+        <v>-25.896</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-8.315</v>
+        <v>-8.167</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-12.342</v>
+        <v>-12.214</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-7.669</v>
+        <v>-6.185</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.766</v>
+        <v>-3.431</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.58</v>
+        <v>-0.789</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>3.993</v>
+        <v>5.181</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.652</v>
+        <v>7.515</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.629</v>
+        <v>8.738</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.519780128454039</v>
+        <v>4.989333953470776</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>8.782805826755427</v>
+        <v>10.03910028310914</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3.195143618596388</v>
+        <v>3.485342019543974</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>11.45924674380307</v>
+        <v>11.69022820112496</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2104,31 +2104,31 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-246.1030383091149</v>
+        <v>-244.3479901868277</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-56.81197048373873</v>
+        <v>-55.80076523640339</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-70.71968828787531</v>
+        <v>-69.98624799449919</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-45.2128286758637</v>
+        <v>-36.46386039382148</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-34.63159424502253</v>
+        <v>-24.93096933585235</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-11.66051660516605</v>
+        <v>-5.822878228782288</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.06869089099054</v>
+        <v>23.44449975111996</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>10.65530957451083</v>
+        <v>30.19406163365342</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>4.937560620756547</v>
+        <v>26.48520853540252</v>
       </c>
       <c r="P30" s="1" t="inlineStr">
         <is>
@@ -6197,46 +6197,46 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>2.999509</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>4.495902</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>5.758</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>7.577</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>8.548999999999999</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>6.547</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>6.471</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>7.272</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>5.515</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>2.274</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>4.863</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>7.109</v>
       </c>
       <c r="P100" s="1" t="inlineStr">
         <is>
@@ -6845,46 +6845,46 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>2.611903</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>1.168291</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>1.399</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>2.112</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>2.221</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>2.041</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="P112" s="1" t="inlineStr">
         <is>
@@ -18591,7 +18591,11 @@
           <t>Depreciation of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -18676,7 +18680,11 @@
           <t>Depreciation of right-of-use assets (note 7)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -19795,7 +19803,11 @@
           <t>Proceeds from sale of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -21324,7 +21336,11 @@
           <t>Proceeds from disposal of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -22962,7 +22978,11 @@
           <t>Depreciation of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -23047,7 +23067,11 @@
           <t>Loss on disposal of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -23136,7 +23160,11 @@
           <t>Depreciation of right-of-use assets (note 6)</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -23227,7 +23255,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -24285,7 +24313,11 @@
           <t>Proceeds from sale of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -25258,7 +25290,11 @@
           <t>Depreciation of property and equipment (note 3)</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -25345,7 +25381,11 @@
           <t>Loss on disposal of property and equipment (note 3)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -25432,7 +25472,11 @@
           <t>Depreciation of right-of-use assets (note 4)</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -25525,7 +25569,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -26421,7 +26465,11 @@
           <t>Proceeds from sale of property and equipment (note 3)</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -27139,7 +27187,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -29307,7 +29355,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -29396,7 +29448,11 @@
           <t>Loss on disposal of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -30304,7 +30360,11 @@
           <t>Proceeds from sale of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -31372,7 +31432,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -32905,7 +32965,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E278" s="5" t="n">
         <v>2.999509</v>
       </c>
@@ -33433,7 +33497,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -38665,7 +38733,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E342" s="5" t="n">
         <v>0.419245</v>
       </c>
@@ -39579,7 +39651,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E352" s="5" t="n">
         <v>2.611903</v>
       </c>
@@ -42235,7 +42311,11 @@
           <t>Depreciation of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -42553,7 +42633,11 @@
           <t>Depreciation of other property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -42638,7 +42722,11 @@
           <t>Depreciation of right-of-use assets (note 7)</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -50631,7 +50719,11 @@
           <t>Depreciation of other property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -50720,7 +50812,11 @@
           <t>Depreciation of right-of-use assets (note 6)</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -50991,7 +51087,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -53127,7 +53223,11 @@
           <t>Depreciation of other property and equipment (note 3)</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
           <t>-</t>
@@ -53305,7 +53405,11 @@
           <t>Depreciation of right-of-use assets (note 4)</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -53398,7 +53502,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -55002,7 +55106,11 @@
           <t>Depreciation of other property and equipment</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E525" t="inlineStr">
         <is>
           <t>-</t>
@@ -55263,7 +55371,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -60768,7 +60876,11 @@
           <t>Depreciation of other property and equipment</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E589" s="5" t="n">
         <v>0.368174</v>
       </c>
